--- a/ksoft_old/docs/records/Expense_Type_Records.xlsx
+++ b/ksoft_old/docs/records/Expense_Type_Records.xlsx
@@ -2886,13 +2886,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3915E06-2BF6-432E-B27B-2B52B569413C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A6C6ED7-0855-4FCC-A7AE-55669EA7DA7D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D26F77E-F179-4FFE-8B4A-05BB0A98AA58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ABF5853-8606-4C1D-9E61-201005A1A086}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC023077-96B1-4EF1-82B0-749A0F9A94FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CBC380C-97DB-422B-9081-734C43DA4BD0}"/>
 </file>
--- a/ksoft_old/docs/records/Expense_Type_Records.xlsx
+++ b/ksoft_old/docs/records/Expense_Type_Records.xlsx
@@ -2886,13 +2886,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A6C6ED7-0855-4FCC-A7AE-55669EA7DA7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{041CA206-A46E-4C70-B2C8-797212289971}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ABF5853-8606-4C1D-9E61-201005A1A086}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D20EEAC-C7A7-4E05-9133-67518FC5C13A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CBC380C-97DB-422B-9081-734C43DA4BD0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5151507F-4A40-499E-ABD1-E73C39FF13BC}"/>
 </file>
--- a/ksoft_old/docs/records/Expense_Type_Records.xlsx
+++ b/ksoft_old/docs/records/Expense_Type_Records.xlsx
@@ -2886,13 +2886,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{041CA206-A46E-4C70-B2C8-797212289971}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3915E06-2BF6-432E-B27B-2B52B569413C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D20EEAC-C7A7-4E05-9133-67518FC5C13A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D26F77E-F179-4FFE-8B4A-05BB0A98AA58}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5151507F-4A40-499E-ABD1-E73C39FF13BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC023077-96B1-4EF1-82B0-749A0F9A94FC}"/>
 </file>